--- a/CVProject_Aggregator_Sheet.xlsx
+++ b/CVProject_Aggregator_Sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jrlop\Downloads\Spring2026\CVProject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jrlop\Downloads\Spring2026\RBD-SLDI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E704A3D1-5F25-4177-9210-2119EFEDD3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB607FFB-0503-43BB-BD37-5964C727CF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Codes" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="47">
   <si>
     <t>Preprocessors:</t>
   </si>
@@ -193,6 +193,15 @@
   <si>
     <t>.</t>
   </si>
+  <si>
+    <t>Max F1</t>
+  </si>
+  <si>
+    <t>Min F1</t>
+  </si>
+  <si>
+    <t>Avg F1</t>
+  </si>
 </sst>
 </file>
 
@@ -256,7 +265,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -284,10 +293,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -11098,7 +11108,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E3AC3BB-FA0F-45B4-851C-C905E31F97F9}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" customWidth="1"/>
@@ -11447,11 +11457,11 @@
         <f t="array" ref="C20">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!I:I, Data!K:K=B9)))</f>
         <v>111</v>
       </c>
-      <c r="D20" s="11" t="str" cm="1">
+      <c r="D20" t="str" cm="1">
         <f t="array" ref="D20">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Q:Q, Data!S:S=B10)))</f>
         <v>112, 142</v>
       </c>
-      <c r="E20" s="12" t="str" cm="1">
+      <c r="E20" s="7" t="str" cm="1">
         <f t="array" ref="E20">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Y:Y, Data!AA:AA=B11)))</f>
         <v>3, 13, 23, 33, 43, 103, 113, 123, 133, 143, 203, 213, 223, 233, 243, 303, 313, 323, 333, 343, 403, 413, 423, 433, 443, 503, 513, 523, 533, 543</v>
       </c>
@@ -11476,11 +11486,11 @@
         <f t="array" ref="C21">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!I:I, Data!K:K=C9)))</f>
         <v>531</v>
       </c>
-      <c r="D21" s="11" t="str" cm="1">
+      <c r="D21" t="str" cm="1">
         <f t="array" ref="D21">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Q:Q, Data!S:S=C10)))</f>
         <v>242</v>
       </c>
-      <c r="E21" s="11" t="str" cm="1">
+      <c r="E21" t="str" cm="1">
         <f t="array" ref="E21">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Y:Y, Data!AA:AA=C11)))</f>
         <v>3, 13, 23, 33, 43, 103, 113, 123, 133, 143, 203, 213, 223, 233, 243, 303, 313, 323, 333, 343, 403, 413, 423, 433, 443, 503, 513, 523, 533, 543</v>
       </c>
@@ -11509,7 +11519,7 @@
         <f t="array" ref="D22">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Q:Q, Data!S:S=D10)))</f>
         <v>112</v>
       </c>
-      <c r="E22" s="11" t="str" cm="1">
+      <c r="E22" t="str" cm="1">
         <f t="array" ref="E22">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Y:Y, Data!AA:AA=D11)))</f>
         <v>3, 13, 23, 33, 43, 103, 113, 123, 133, 143, 203, 213, 223, 233, 243, 303, 313, 323, 333, 343, 403, 413, 423, 433, 443, 503, 513, 523, 533, 543</v>
       </c>
@@ -11538,7 +11548,7 @@
         <f t="array" ref="D23">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Q:Q, Data!S:S=E10)))</f>
         <v>112</v>
       </c>
-      <c r="E23" s="11" t="str" cm="1">
+      <c r="E23" t="str" cm="1">
         <f t="array" ref="E23">_xlfn.TEXTJOIN(", ", TRUE, _xlfn.UNIQUE(_xlfn._xlws.FILTER(Data!Y:Y, Data!AA:AA=E11)))</f>
         <v>3, 13, 23, 33, 43, 103, 113, 123, 133, 143, 203, 213, 223, 233, 243, 303, 313, 323, 333, 343, 403, 413, 423, 433, 443, 503, 513, 523, 533, 543</v>
       </c>
@@ -11552,7 +11562,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="11" t="s">
         <v>42</v>
       </c>
       <c r="B25" s="6" t="s">
@@ -11643,6 +11653,86 @@
       </c>
       <c r="E29" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31" s="12"/>
+      <c r="B31" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" cm="1">
+        <f t="array" ref="B32">(MAX(IF(MOD(ROW(Data!G5:G121)-MIN(ROW(Data!G5:G121)),4)=0,Data!G5:G121)))</f>
+        <v>0.80220000000000002</v>
+      </c>
+      <c r="C32" cm="1">
+        <f t="array" ref="C32">(AVERAGE(IF(MOD(ROW(Data!C5:C121)-MIN(ROW(Data!C5:C121)),4)=0,Data!C5:C121)))</f>
+        <v>0.35636333333333342</v>
+      </c>
+      <c r="D32" cm="1">
+        <f t="array" ref="D32">(MIN(IF(MOD(ROW(Data!F5:F121)-MIN(ROW(Data!F5:F121)),4)=0,Data!F5:F121)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" cm="1">
+        <f t="array" ref="B33">(MAX(IF(MOD(ROW(Data!O5:O121)-MIN(ROW(Data!O5:O121)),4)=0,Data!O5:O121)))</f>
+        <v>0.80269999999999997</v>
+      </c>
+      <c r="C33" cm="1">
+        <f t="array" ref="C33">(AVERAGE(IF(MOD(ROW(Data!K5:K121)-MIN(ROW(Data!K5:K121)),4)=0,Data!K5:K121)))</f>
+        <v>0.35617666666666659</v>
+      </c>
+      <c r="D33" cm="1">
+        <f t="array" ref="D33">(MIN(IF(MOD(ROW(Data!N5:N121)-MIN(ROW(Data!N5:N121)),4)=0,Data!N5:N121)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" cm="1">
+        <f t="array" ref="B34">(MAX(IF(MOD(ROW(Data!W5:W121)-MIN(ROW(Data!W5:W121)),4)=0,Data!W5:W121)))</f>
+        <v>0.77100000000000002</v>
+      </c>
+      <c r="C34" cm="1">
+        <f t="array" ref="C34">(AVERAGE(IF(MOD(ROW(Data!S5:S121)-MIN(ROW(Data!S5:S121)),4)=0,Data!S5:S121)))</f>
+        <v>0.37745666666666655</v>
+      </c>
+      <c r="D34" cm="1">
+        <f t="array" ref="D34">(MIN(IF(MOD(ROW(Data!V5:V121)-MIN(ROW(Data!V5:V121)),4)=0,Data!V5:V121)))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" cm="1">
+        <f t="array" ref="B35">(MAX(IF(MOD(ROW(Data!AE5:AE121)-MIN(ROW(Data!AE5:AE121)),4)=0,Data!AE5:AE121)))</f>
+        <v>0.52210000000000001</v>
+      </c>
+      <c r="C35" cm="1">
+        <f t="array" ref="C35">(AVERAGE(IF(MOD(ROW(Data!AA5:AA121)-MIN(ROW(Data!AA5:AA121)),4)=0,Data!AA5:AA121)))</f>
+        <v>0.39409999999999995</v>
+      </c>
+      <c r="D35" cm="1">
+        <f t="array" ref="D35">(MIN(IF(MOD(ROW(Data!AD5:AD121)-MIN(ROW(Data!AD5:AD121)),4)=0,Data!AD5:AD121)))</f>
+        <v>0.37590000000000001</v>
       </c>
     </row>
   </sheetData>
